--- a/data/Семинары(Биоинженеры).xlsx
+++ b/data/Семинары(Биоинженеры).xlsx
@@ -1418,7 +1418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1431,8 +1431,11 @@
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1445,8 +1448,11 @@
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="E3">
+        <v>0.8</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1459,8 +1465,11 @@
       <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="E4">
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1473,8 +1482,11 @@
       <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="E5">
+        <v>1.1</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -1487,8 +1499,11 @@
       <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="E6">
+        <v>1.2</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1501,8 +1516,11 @@
       <c r="D7" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
@@ -1515,8 +1533,11 @@
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="E8">
+        <v>1.1</v>
+      </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -1529,8 +1550,11 @@
       <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1542,6 +1566,9 @@
       </c>
       <c r="D10" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="E10">
+        <v>1.1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1558,7 +1585,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -1570,6 +1597,9 @@
       </c>
       <c r="D12" s="2" t="s">
         <v>48</v>
+      </c>
+      <c r="E12">
+        <v>1.5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1614,7 +1644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
         <v>60</v>
       </c>
@@ -1627,8 +1657,11 @@
       <c r="D16" s="2" t="s">
         <v>63</v>
       </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
@@ -1640,6 +1673,9 @@
       </c>
       <c r="D17" s="2" t="s">
         <v>66</v>
+      </c>
+      <c r="E17">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/Семинары(Биоинженеры).xlsx
+++ b/data/Семинары(Биоинженеры).xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
   <si>
     <t>Family</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>st097958</t>
+  </si>
+  <si>
+    <t>Пак</t>
+  </si>
+  <si>
+    <t>Глеб</t>
   </si>
 </sst>
 </file>
@@ -1389,7 +1395,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.8888888888889" customWidth="1"/>
@@ -1418,7 +1424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1434,8 +1440,11 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1451,8 +1460,11 @@
       <c r="E3">
         <v>0.8</v>
       </c>
+      <c r="F3">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -1468,8 +1480,11 @@
       <c r="E4">
         <v>0.9</v>
       </c>
+      <c r="F4">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1485,8 +1500,11 @@
       <c r="E5">
         <v>1.1</v>
       </c>
+      <c r="F5">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -1502,8 +1520,11 @@
       <c r="E6">
         <v>1.2</v>
       </c>
+      <c r="F6">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1519,8 +1540,11 @@
       <c r="E7">
         <v>1</v>
       </c>
+      <c r="F7">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
@@ -1536,8 +1560,11 @@
       <c r="E8">
         <v>1.1</v>
       </c>
+      <c r="F8">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -1553,8 +1580,11 @@
       <c r="E9">
         <v>1</v>
       </c>
+      <c r="F9">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -1569,6 +1599,9 @@
       </c>
       <c r="E10">
         <v>1.1</v>
+      </c>
+      <c r="F10">
+        <v>1.5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1585,7 +1618,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
@@ -1599,6 +1632,9 @@
         <v>48</v>
       </c>
       <c r="E12">
+        <v>1.5</v>
+      </c>
+      <c r="F12">
         <v>1.5</v>
       </c>
     </row>
@@ -1630,7 +1666,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
@@ -1643,8 +1679,11 @@
       <c r="D15" s="2" t="s">
         <v>59</v>
       </c>
+      <c r="F15">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>60</v>
       </c>
@@ -1660,8 +1699,11 @@
       <c r="E16">
         <v>1</v>
       </c>
+      <c r="F16">
+        <v>1.5</v>
+      </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
@@ -1676,6 +1718,17 @@
       </c>
       <c r="E17">
         <v>1.3</v>
+      </c>
+      <c r="F17">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
